--- a/diseases/d063/2026-2029.xlsx
+++ b/diseases/d063/2026-2029.xlsx
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4518,13 +4518,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>337</v>
+        <v>852</v>
       </c>
       <c r="O27" t="n">
-        <v>337</v>
+        <v>852</v>
       </c>
       <c r="R27" t="n">
-        <v>1.237737583178169</v>
+        <v>3.129235670230861</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -4673,10 +4673,10 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>337</v>
+        <v>852</v>
       </c>
       <c r="O28" t="n">
-        <v>337</v>
+        <v>852</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN38" t="b">
@@ -6507,7 +6507,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8764</v>
+        <v>9279</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d063/2026-2029.xlsx
+++ b/diseases/d063/2026-2029.xlsx
@@ -4518,13 +4518,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="O27" t="n">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="R27" t="n">
-        <v>3.129235670230861</v>
+        <v>3.132908482050381</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -4673,10 +4673,10 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="O28" t="n">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9279</v>
+        <v>9280</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d063/2026-2029.xlsx
+++ b/diseases/d063/2026-2029.xlsx
@@ -4518,13 +4518,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="O27" t="n">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="R27" t="n">
-        <v>3.132908482050381</v>
+        <v>3.14392691750894</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -4673,10 +4673,10 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="O28" t="n">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9280</v>
+        <v>9283</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d063/2026-2029.xlsx
+++ b/diseases/d063/2026-2029.xlsx
@@ -3029,13 +3029,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="O17" t="n">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="R17" t="n">
-        <v>3.188000659343178</v>
+        <v>3.191673471162698</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="O18" t="n">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -4518,13 +4518,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>856</v>
+        <v>868</v>
       </c>
       <c r="O27" t="n">
-        <v>856</v>
+        <v>868</v>
       </c>
       <c r="R27" t="n">
-        <v>3.14392691750894</v>
+        <v>3.188000659343178</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -4673,10 +4673,10 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>856</v>
+        <v>868</v>
       </c>
       <c r="O28" t="n">
-        <v>856</v>
+        <v>868</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9283</v>
+        <v>9296</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d063/2026-2029.xlsx
+++ b/diseases/d063/2026-2029.xlsx
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -3029,13 +3029,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="O17" t="n">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="R17" t="n">
-        <v>3.191673471162698</v>
+        <v>3.213710342079816</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="O18" t="n">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4518,13 +4518,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>868</v>
+        <v>889</v>
       </c>
       <c r="O27" t="n">
-        <v>868</v>
+        <v>889</v>
       </c>
       <c r="R27" t="n">
-        <v>3.188000659343178</v>
+        <v>3.265129707553093</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -4673,10 +4673,10 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>868</v>
+        <v>889</v>
       </c>
       <c r="O28" t="n">
-        <v>868</v>
+        <v>889</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -6507,7 +6507,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9296</v>
+        <v>9323</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d063/2026-2029.xlsx
+++ b/diseases/d063/2026-2029.xlsx
@@ -4518,13 +4518,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="O27" t="n">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="R27" t="n">
-        <v>3.265129707553093</v>
+        <v>3.268802519372613</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -4673,10 +4673,10 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="O28" t="n">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -6007,13 +6007,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>13</v>
+        <v>768</v>
       </c>
       <c r="O37" t="n">
-        <v>13</v>
+        <v>768</v>
       </c>
       <c r="R37" t="n">
-        <v>0.04774655365375727</v>
+        <v>2.820719477391199</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -6162,10 +6162,10 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>13</v>
+        <v>768</v>
       </c>
       <c r="O38" t="n">
-        <v>13</v>
+        <v>768</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9323</v>
+        <v>10079</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d063/2026-2029.xlsx
+++ b/diseases/d063/2026-2029.xlsx
@@ -4518,13 +4518,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="O27" t="n">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="R27" t="n">
-        <v>3.268802519372613</v>
+        <v>3.287166578470212</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -4673,10 +4673,10 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="O28" t="n">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -6007,13 +6007,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>768</v>
+        <v>785</v>
       </c>
       <c r="O37" t="n">
-        <v>768</v>
+        <v>785</v>
       </c>
       <c r="R37" t="n">
-        <v>2.820719477391199</v>
+        <v>2.883157278323035</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -6162,10 +6162,10 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>768</v>
+        <v>785</v>
       </c>
       <c r="O38" t="n">
-        <v>768</v>
+        <v>785</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10079</v>
+        <v>10101</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d063/2026-2029.xlsx
+++ b/diseases/d063/2026-2029.xlsx
@@ -23870,13 +23870,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>895</v>
+        <v>905</v>
       </c>
       <c r="O123" t="n">
-        <v>895</v>
+        <v>905</v>
       </c>
       <c r="R123" t="n">
-        <v>3.287166578470212</v>
+        <v>3.32389469666541</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -24025,10 +24025,10 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>895</v>
+        <v>905</v>
       </c>
       <c r="O124" t="n">
-        <v>895</v>
+        <v>905</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
@@ -27335,13 +27335,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>817</v>
+        <v>848</v>
       </c>
       <c r="O141" t="n">
-        <v>817</v>
+        <v>848</v>
       </c>
       <c r="R141" t="n">
-        <v>3.000687256547669</v>
+        <v>3.114544422952782</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -27490,10 +27490,10 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>817</v>
+        <v>848</v>
       </c>
       <c r="O142" t="n">
-        <v>817</v>
+        <v>848</v>
       </c>
       <c r="U142" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15619</v>
+        <v>15660</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d063/2026-2029.xlsx
+++ b/diseases/d063/2026-2029.xlsx
@@ -23870,13 +23870,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="O123" t="n">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="R123" t="n">
-        <v>3.32389469666541</v>
+        <v>3.331240320304449</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -24025,10 +24025,10 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="O124" t="n">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
@@ -27335,13 +27335,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="O141" t="n">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="R141" t="n">
-        <v>3.114544422952782</v>
+        <v>3.188000659343178</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -27490,10 +27490,10 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="O142" t="n">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="U142" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15660</v>
+        <v>15682</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d063/2026-2029.xlsx
+++ b/diseases/d063/2026-2029.xlsx
@@ -27335,13 +27335,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="O141" t="n">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="R141" t="n">
-        <v>3.188000659343178</v>
+        <v>3.213710342079816</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -27490,10 +27490,10 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="O142" t="n">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="U142" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15682</v>
+        <v>15689</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d063/2026-2029.xlsx
+++ b/diseases/d063/2026-2029.xlsx
@@ -1151,7 +1151,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7627,7 +7627,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9552,7 +9552,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10322,7 +10322,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12402,7 +12402,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12787,7 +12787,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13172,7 +13172,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13557,7 +13557,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14097,7 +14097,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14482,7 +14482,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -14867,7 +14867,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -15252,7 +15252,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15637,7 +15637,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -16022,7 +16022,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -16407,7 +16407,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16792,7 +16792,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -17177,7 +17177,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -17562,7 +17562,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -17947,7 +17947,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -18332,7 +18332,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -18717,7 +18717,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -19102,7 +19102,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19487,7 +19487,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -19872,7 +19872,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -20257,7 +20257,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -21027,7 +21027,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -21412,7 +21412,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21797,7 +21797,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -22182,7 +22182,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22567,7 +22567,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -22952,7 +22952,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -23337,7 +23337,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -23722,7 +23722,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -24107,7 +24107,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -24492,7 +24492,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -25262,7 +25262,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -25647,7 +25647,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -26032,7 +26032,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -26417,7 +26417,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -26802,7 +26802,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -27187,7 +27187,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -27335,13 +27335,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="O141" t="n">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="R141" t="n">
-        <v>3.213710342079816</v>
+        <v>3.235747212996935</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -27490,10 +27490,10 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="O142" t="n">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="U142" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27957,7 +27957,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28342,7 +28342,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -29112,7 +29112,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -29497,7 +29497,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -29882,7 +29882,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -30267,7 +30267,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30652,7 +30652,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -30915,7 +30915,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15689</v>
+        <v>15695</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d063/2026-2029.xlsx
+++ b/diseases/d063/2026-2029.xlsx
@@ -10845,13 +10845,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="O74" t="n">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="R74" t="n">
-        <v>3.254111272094534</v>
+        <v>3.265129707553093</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15699</v>
+        <v>15702</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d063/2026-2029.xlsx
+++ b/diseases/d063/2026-2029.xlsx
@@ -10845,13 +10845,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="O74" t="n">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="R74" t="n">
-        <v>3.265129707553093</v>
+        <v>3.276148143011653</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
@@ -12037,6 +12037,146 @@
         </is>
       </c>
       <c r="BC82" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D063</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>zoster</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Zoster</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D063</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Zoster</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>带状疱疹</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>557</v>
+      </c>
+      <c r="O83" t="n">
+        <v>557</v>
+      </c>
+      <c r="R83" t="n">
+        <v>2.045756183472523</v>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_ZOSTER</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_ZOSTER</t>
+        </is>
+      </c>
+      <c r="AT83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -12075,7 +12215,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -12158,7 +12298,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10">
@@ -12168,7 +12308,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11">
@@ -12220,7 +12360,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15702</v>
+        <v>16262</v>
       </c>
     </row>
     <row r="16">
